--- a/sMSA_Supplementary_DataS2.xlsx
+++ b/sMSA_Supplementary_DataS2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q87z649\Documents\DATA\Beck, Ashley\22_MRE\suppFiles\January 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AA8B10-44DC-40F4-A9AD-FC4B9E1B027F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2FA45D-1285-454A-90D7-1F5BD6ED891C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1830" windowWidth="18900" windowHeight="13410" xr2:uid="{C9082305-17D1-4869-843C-4336A5FCDFA4}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{C9082305-17D1-4869-843C-4336A5FCDFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="DataS2" sheetId="9" r:id="rId1"/>
@@ -358,9 +358,6 @@
       </rPr>
       <t>corresponding author: R.P.C., Email: rossc@montana.edu</t>
     </r>
-  </si>
-  <si>
-    <t>Cell Geometry and Membrane Protein Crowding Constrain Growth Rate, Overflow Metabolism, Respiration, and Maintenance Energy</t>
   </si>
   <si>
     <t>cell/g</t>
@@ -850,6 +847,9 @@
   </si>
   <si>
     <t>black data: surface are, right axis</t>
+  </si>
+  <si>
+    <t>Cell Geometry and Membrane Protein Crowding Constrain Escherichia coli Growth Rate, Overflow Metabolism, Respiration, and Maintenance Energy</t>
   </si>
 </sst>
 </file>
@@ -13282,12 +13282,12 @@
     </row>
     <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B6" s="36" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="B7" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="38"/>
       <c r="D7" s="38"/>
@@ -13317,7 +13317,7 @@
     </row>
     <row r="10" spans="1:7" s="33" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10" s="38"/>
       <c r="D10" s="39"/>
@@ -13327,7 +13327,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -13337,7 +13337,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="38"/>
       <c r="D12" s="38"/>
@@ -13347,7 +13347,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="38"/>
       <c r="D13" s="38"/>
@@ -13388,7 +13388,7 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
@@ -13396,7 +13396,7 @@
         <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -13587,10 +13587,10 @@
         <v>2</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V27" s="26"/>
       <c r="W27" s="4"/>
@@ -15135,10 +15135,10 @@
         <v>2</v>
       </c>
       <c r="T60" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="U60" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:36" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -16525,7 +16525,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>6</v>
@@ -16572,37 +16572,37 @@
         <v>19</v>
       </c>
       <c r="N2" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="P2" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="Q2" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="Q2" s="28" t="s">
+      <c r="R2" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="R2" s="43" t="s">
+      <c r="S2" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="S2" s="28" t="s">
+      <c r="T2" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="T2" s="28" t="s">
+      <c r="U2" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="U2" s="28" t="s">
+      <c r="V2" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="V2" s="28" t="s">
+      <c r="W2" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="W2" s="28" t="s">
+      <c r="X2" s="28" t="s">
         <v>69</v>
-      </c>
-      <c r="X2" s="28" t="s">
-        <v>70</v>
       </c>
       <c r="Y2" s="28" t="s">
         <v>13</v>
@@ -16610,22 +16610,22 @@
     </row>
     <row r="3" spans="1:25" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="C3" s="19" t="s">
         <v>73</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>74</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>76</v>
       </c>
       <c r="G3" s="17">
         <v>0.75304000000000004</v>
@@ -16676,7 +16676,7 @@
         <v>0.64227999999999996</v>
       </c>
       <c r="W3" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X3" s="17">
         <v>0.23172999999999999</v>
@@ -16687,7 +16687,7 @@
     </row>
     <row r="4" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F4" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" s="17">
         <v>0.77830999999999995</v>
@@ -16738,7 +16738,7 @@
         <v>0.46503</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X4" s="17">
         <v>0.22339999999999999</v>
@@ -16749,7 +16749,7 @@
     </row>
     <row r="5" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F5" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" s="17">
         <v>0.71421999999999997</v>
@@ -16800,7 +16800,7 @@
         <v>0.53339999999999999</v>
       </c>
       <c r="W5" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X5" s="17">
         <v>0.22388</v>
@@ -16811,7 +16811,7 @@
     </row>
     <row r="6" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F6" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="17">
         <v>0.75836999999999999</v>
@@ -16862,7 +16862,7 @@
         <v>0.39051000000000002</v>
       </c>
       <c r="W6" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X6" s="17">
         <v>0.21720999999999999</v>
@@ -16873,7 +16873,7 @@
     </row>
     <row r="7" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F7" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" s="17">
         <v>0.71797</v>
@@ -16924,7 +16924,7 @@
         <v>0.57887999999999995</v>
       </c>
       <c r="W7" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X7" s="17">
         <v>0.23143</v>
@@ -16935,7 +16935,7 @@
     </row>
     <row r="8" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F8" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G8" s="17">
         <v>0.68576999999999999</v>
@@ -16986,7 +16986,7 @@
         <v>0.68157999999999996</v>
       </c>
       <c r="W8" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X8" s="17">
         <v>0.22600999999999999</v>
@@ -16997,7 +16997,7 @@
     </row>
     <row r="9" spans="1:25" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F9" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G9" s="21">
         <v>0.69311</v>
@@ -17048,7 +17048,7 @@
         <v>0.50502999999999998</v>
       </c>
       <c r="W9" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X9" s="21">
         <v>0.21523</v>
@@ -17059,22 +17059,22 @@
     </row>
     <row r="10" spans="1:25" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="C10" s="19" t="s">
         <v>85</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>76</v>
       </c>
       <c r="G10" s="17">
         <v>0.71348999999999996</v>
@@ -17128,7 +17128,7 @@
         <v>162270</v>
       </c>
       <c r="X10" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y10" s="17">
         <v>0.71348999999999996</v>
@@ -17136,7 +17136,7 @@
     </row>
     <row r="11" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F11" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11" s="17">
         <v>0.73780000000000001</v>
@@ -17190,7 +17190,7 @@
         <v>127600</v>
       </c>
       <c r="X11" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y11" s="17">
         <v>0.73780000000000001</v>
@@ -17198,7 +17198,7 @@
     </row>
     <row r="12" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F12" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" s="17">
         <v>0.75053000000000003</v>
@@ -17252,7 +17252,7 @@
         <v>126320</v>
       </c>
       <c r="X12" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y12" s="17">
         <v>0.75053000000000003</v>
@@ -17260,7 +17260,7 @@
     </row>
     <row r="13" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F13" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13" s="17">
         <v>0.76639999999999997</v>
@@ -17314,7 +17314,7 @@
         <v>131080</v>
       </c>
       <c r="X13" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y13" s="17">
         <v>0.76639999999999997</v>
@@ -17322,7 +17322,7 @@
     </row>
     <row r="14" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F14" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G14" s="17">
         <v>0.73590999999999995</v>
@@ -17376,7 +17376,7 @@
         <v>124960</v>
       </c>
       <c r="X14" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y14" s="17">
         <v>0.73590999999999995</v>
@@ -17384,7 +17384,7 @@
     </row>
     <row r="15" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F15" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G15" s="17">
         <v>0.68476999999999999</v>
@@ -17438,7 +17438,7 @@
         <v>99143</v>
       </c>
       <c r="X15" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y15" s="17">
         <v>0.68476999999999999</v>
@@ -17446,7 +17446,7 @@
     </row>
     <row r="16" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F16" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G16" s="17">
         <v>0.69496000000000002</v>
@@ -17500,7 +17500,7 @@
         <v>120280</v>
       </c>
       <c r="X16" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y16" s="17">
         <v>0.69496000000000002</v>
@@ -17508,7 +17508,7 @@
     </row>
     <row r="17" spans="1:25" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F17" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="21">
         <v>0.70050999999999997</v>
@@ -17562,7 +17562,7 @@
         <v>96928</v>
       </c>
       <c r="X17" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y17" s="21">
         <v>0.70050999999999997</v>
@@ -17570,7 +17570,7 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:25" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -17637,7 +17637,7 @@
         <v>0.35415000000000002</v>
       </c>
       <c r="W19" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X19" s="17">
         <v>0.2878</v>
@@ -17710,7 +17710,7 @@
         <v>0.44861000000000001</v>
       </c>
       <c r="W20" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X20" s="17">
         <v>0.28744999999999998</v>
@@ -17735,32 +17735,32 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
         <v>101</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>102</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>103</v>
-      </c>
-      <c r="L3" t="s">
-        <v>104</v>
       </c>
       <c r="N3" t="s">
         <v>2</v>
@@ -17768,33 +17768,33 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" t="s">
         <v>105</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>106</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" t="s">
+        <v>106</v>
+      </c>
+      <c r="N4" t="s">
         <v>107</v>
-      </c>
-      <c r="H4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" t="s">
-        <v>107</v>
-      </c>
-      <c r="J4" t="s">
-        <v>106</v>
-      </c>
-      <c r="K4" t="s">
-        <v>107</v>
-      </c>
-      <c r="N4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5">
         <v>0.88</v>
@@ -17828,7 +17828,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E6">
         <v>0.73</v>
@@ -17862,7 +17862,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7">
         <v>0.61</v>
@@ -17896,7 +17896,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8">
         <v>0.4</v>
@@ -17930,7 +17930,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E9">
         <v>0.24</v>
@@ -17964,7 +17964,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -18000,7 +18000,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B11" s="44"/>
       <c r="C11" s="44"/>
@@ -18036,7 +18036,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
@@ -18072,7 +18072,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -18108,7 +18108,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" s="44"/>
       <c r="C14" s="44"/>
@@ -18144,7 +18144,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B15" s="44"/>
       <c r="C15" s="44"/>
@@ -18180,27 +18180,27 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K17" t="s">
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AB17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="L18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
@@ -18230,26 +18230,26 @@
     </row>
     <row r="35" spans="6:20" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="6:20" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="6:20" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
